--- a/healthcare_forms/021_surgery_scheduling_information_form--healthcare_forms.xlsx
+++ b/healthcare_forms/021_surgery_scheduling_information_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -983,7 +983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1033,29 +1033,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>surgery_scheduling_information_form</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Surgery Scheduling Information Form</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>patient_status_choices</t>
+          <t>emergency_contact_relationship_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>surgery_scheduling_information_form</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Surgery Scheduling Information Form</t>
+          <t>Mother</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mother</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Father</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>father</t>
+          <t>brother</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Brother</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>brother</t>
+          <t>sister</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sister</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>spouse</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Partner</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>son</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Son</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>son</t>
+          <t>daughter</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Daughter</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>daughter</t>
+          <t>son-in-law</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Son-in-law</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>son-in-law</t>
+          <t>daughter-in-law</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Son-in-law</t>
+          <t>Daughter-in-law</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>daughter-in-law</t>
+          <t>grandson</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Daughter-in-law</t>
+          <t>Grandson</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>grandson</t>
+          <t>granddaughter</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Grandson</t>
+          <t>Granddaughter</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>granddaughter</t>
+          <t>grandson-in-law</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Granddaughter</t>
+          <t>Grandson-in-law</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>grandson-in-law</t>
+          <t>granddaughter-in-law</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Grandson-in-law</t>
+          <t>Granddaughter-in-law</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>granddaughter-in-law</t>
+          <t>nephew</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Granddaughter-in-law</t>
+          <t>Nephew</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nephew</t>
+          <t>niece</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nephew</t>
+          <t>Niece</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>niece</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Niece</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>parent</t>
+          <t>parent's_parent</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Parent</t>
+          <t>Parent's Parent</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>parent's_parent</t>
+          <t>sibling</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Parent's Parent</t>
+          <t>Sibling</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sibling</t>
+          <t>spouse's_parent</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sibling</t>
+          <t>Spouse's Parent</t>
         </is>
       </c>
     </row>
@@ -1390,29 +1390,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>spouse's_parent</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spouse's Parent</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship_choices</t>
+          <t>procedure_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1424,29 +1424,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>procedure_choices</t>
+          <t>anesthesia_type_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1458,29 +1458,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>anesthesia_type_choices</t>
+          <t>surgeon_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1492,27 +1492,10 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>surgeon_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
